--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46269.01041666666</v>
+        <v>46278.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46269.02083333334</v>
+        <v>46278.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46269.03125</v>
+        <v>46278.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46269.04166666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46269.05208333334</v>
+        <v>46278.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46269.0625</v>
+        <v>46278.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46269.07291666666</v>
+        <v>46278.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46269.08333333334</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46269.09375</v>
+        <v>46278.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46269.10416666666</v>
+        <v>46278.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46269.11458333334</v>
+        <v>46278.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46269.125</v>
+        <v>46278.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46269.13541666666</v>
+        <v>46278.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46269.14583333334</v>
+        <v>46278.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46269.15625</v>
+        <v>46278.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46269.16666666666</v>
+        <v>46278.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46269.17708333334</v>
+        <v>46278.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46269.1875</v>
+        <v>46278.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46269.19791666666</v>
+        <v>46278.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46269.20833333334</v>
+        <v>46278.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46269.21875</v>
+        <v>46278.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46269.22916666666</v>
+        <v>46278.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -578,186 +578,98 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46269.23958333334</v>
+        <v>46278.23958333334</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46269.25</v>
+        <v>46278.25</v>
       </c>
       <c r="B26">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46269.26041666666</v>
+        <v>46278.26041666666</v>
       </c>
       <c r="B27">
-        <v>86</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46269.27083333334</v>
+        <v>46278.27083333334</v>
       </c>
       <c r="B28">
-        <v>189</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46269.28125</v>
+        <v>46278.28125</v>
       </c>
       <c r="B29">
-        <v>335</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46269.29166666666</v>
+        <v>46278.29166666666</v>
       </c>
       <c r="B30">
-        <v>532</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46269.30208333334</v>
+        <v>46278.30208333334</v>
       </c>
       <c r="B31">
-        <v>752</v>
+        <v>270</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46269.3125</v>
+        <v>46278.3125</v>
       </c>
       <c r="B32">
-        <v>1021</v>
+        <v>356</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46269.32291666666</v>
+        <v>46278.32291666666</v>
       </c>
       <c r="B33">
-        <v>1359</v>
+        <v>420</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46269.33333333334</v>
+        <v>46278.33333333334</v>
       </c>
       <c r="B34">
-        <v>1687</v>
+        <v>547</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46269.34375</v>
+        <v>46278.34375</v>
       </c>
       <c r="B35">
-        <v>1827</v>
+        <v>674</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46269.35416666666</v>
+        <v>46278.35416666666</v>
       </c>
       <c r="B36">
-        <v>1966</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="2">
-        <v>46269.36458333334</v>
-      </c>
-      <c r="B37">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="2">
-        <v>46269.375</v>
-      </c>
-      <c r="B38">
-        <v>2292</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="2">
-        <v>46269.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>2397</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="2">
-        <v>46269.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>2601</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="2">
-        <v>46269.40625</v>
-      </c>
-      <c r="B41">
-        <v>2764</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="2">
-        <v>46269.41666666666</v>
-      </c>
-      <c r="B42">
-        <v>2885</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="2">
-        <v>46269.42708333334</v>
-      </c>
-      <c r="B43">
-        <v>3022</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="2">
-        <v>46269.4375</v>
-      </c>
-      <c r="B44">
-        <v>3076</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="2">
-        <v>46269.44791666666</v>
-      </c>
-      <c r="B45">
-        <v>3076</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="2">
-        <v>46269.45833333334</v>
-      </c>
-      <c r="B46">
-        <v>3148</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="2">
-        <v>46269.46875</v>
-      </c>
-      <c r="B47">
-        <v>3038</v>
+        <v>850</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46278</v>
+        <v>46283</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46278.01041666666</v>
+        <v>46283.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46278.02083333334</v>
+        <v>46283.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46278.03125</v>
+        <v>46283.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46278.04166666666</v>
+        <v>46283.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46278.05208333334</v>
+        <v>46283.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46278.0625</v>
+        <v>46283.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46278.07291666666</v>
+        <v>46283.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46278.08333333334</v>
+        <v>46283.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46278.09375</v>
+        <v>46283.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46278.10416666666</v>
+        <v>46283.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46278.11458333334</v>
+        <v>46283.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46278.125</v>
+        <v>46283.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46278.13541666666</v>
+        <v>46283.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46278.14583333334</v>
+        <v>46283.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46278.15625</v>
+        <v>46283.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46278.16666666666</v>
+        <v>46283.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46278.17708333334</v>
+        <v>46283.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46278.1875</v>
+        <v>46283.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46278.19791666666</v>
+        <v>46283.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46278.20833333334</v>
+        <v>46283.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46278.21875</v>
+        <v>46283.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46278.22916666666</v>
+        <v>46283.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46278.23958333334</v>
+        <v>46283.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -586,90 +586,130 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46278.25</v>
+        <v>46283.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46278.26041666666</v>
+        <v>46283.26041666666</v>
       </c>
       <c r="B27">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46278.27083333334</v>
+        <v>46283.27083333334</v>
       </c>
       <c r="B28">
-        <v>34</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46278.28125</v>
+        <v>46283.28125</v>
       </c>
       <c r="B29">
-        <v>100</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46278.29166666666</v>
+        <v>46283.29166666666</v>
       </c>
       <c r="B30">
-        <v>179</v>
+        <v>448</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46278.30208333334</v>
+        <v>46283.30208333334</v>
       </c>
       <c r="B31">
-        <v>270</v>
+        <v>622</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46278.3125</v>
+        <v>46283.3125</v>
       </c>
       <c r="B32">
-        <v>356</v>
+        <v>622</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46278.32291666666</v>
+        <v>46283.32291666666</v>
       </c>
       <c r="B33">
-        <v>420</v>
+        <v>998</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46278.33333333334</v>
+        <v>46283.33333333334</v>
       </c>
       <c r="B34">
-        <v>547</v>
+        <v>998</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46278.34375</v>
+        <v>46283.34375</v>
       </c>
       <c r="B35">
-        <v>674</v>
+        <v>998</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46278.35416666666</v>
+        <v>46283.35416666666</v>
       </c>
       <c r="B36">
-        <v>850</v>
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2">
+        <v>46283.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2">
+        <v>46283.375</v>
+      </c>
+      <c r="B38">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2">
+        <v>46283.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="2">
+        <v>46283.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="2">
+        <v>46283.40625</v>
+      </c>
+      <c r="B41">
+        <v>2062</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46283.01041666666</v>
+        <v>46285.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46283.02083333334</v>
+        <v>46285.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46283.03125</v>
+        <v>46285.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46283.04166666666</v>
+        <v>46285.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46283.05208333334</v>
+        <v>46285.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46283.0625</v>
+        <v>46285.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46283.07291666666</v>
+        <v>46285.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46283.08333333334</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46283.09375</v>
+        <v>46285.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46283.10416666666</v>
+        <v>46285.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46283.11458333334</v>
+        <v>46285.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46283.125</v>
+        <v>46285.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46283.13541666666</v>
+        <v>46285.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46283.14583333334</v>
+        <v>46285.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46283.15625</v>
+        <v>46285.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46283.16666666666</v>
+        <v>46285.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46283.17708333334</v>
+        <v>46285.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46283.1875</v>
+        <v>46285.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46283.19791666666</v>
+        <v>46285.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46283.20833333334</v>
+        <v>46285.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46283.21875</v>
+        <v>46285.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46283.22916666666</v>
+        <v>46285.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46283.23958333334</v>
+        <v>46285.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -586,130 +586,114 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46283.25</v>
+        <v>46285.25</v>
       </c>
       <c r="B26">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46283.26041666666</v>
+        <v>46285.26041666666</v>
       </c>
       <c r="B27">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46283.27083333334</v>
+        <v>46285.27083333334</v>
       </c>
       <c r="B28">
-        <v>132</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46283.28125</v>
+        <v>46285.28125</v>
       </c>
       <c r="B29">
-        <v>273</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46283.29166666666</v>
+        <v>46285.29166666666</v>
       </c>
       <c r="B30">
-        <v>448</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46283.30208333334</v>
+        <v>46285.30208333334</v>
       </c>
       <c r="B31">
-        <v>622</v>
+        <v>529</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46283.3125</v>
+        <v>46285.3125</v>
       </c>
       <c r="B32">
-        <v>622</v>
+        <v>729</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46283.32291666666</v>
+        <v>46285.32291666666</v>
       </c>
       <c r="B33">
-        <v>998</v>
+        <v>938</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46283.33333333334</v>
+        <v>46285.33333333334</v>
       </c>
       <c r="B34">
-        <v>998</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46283.34375</v>
+        <v>46285.34375</v>
       </c>
       <c r="B35">
-        <v>998</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46283.35416666666</v>
+        <v>46285.35416666666</v>
       </c>
       <c r="B36">
-        <v>1554</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46283.36458333334</v>
+        <v>46285.36458333334</v>
       </c>
       <c r="B37">
-        <v>1704</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46283.375</v>
+        <v>46285.375</v>
       </c>
       <c r="B38">
-        <v>1813</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46283.38541666666</v>
+        <v>46285.38541666666</v>
       </c>
       <c r="B39">
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="2">
-        <v>46283.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="2">
-        <v>46283.40625</v>
-      </c>
-      <c r="B41">
-        <v>2062</v>
+        <v>1912</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46285</v>
+        <v>46295</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46285.01041666666</v>
+        <v>46295.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46285.02083333334</v>
+        <v>46295.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46285.03125</v>
+        <v>46295.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46285.04166666666</v>
+        <v>46295.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46285.05208333334</v>
+        <v>46295.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46285.0625</v>
+        <v>46295.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46285.07291666666</v>
+        <v>46295.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46285.08333333334</v>
+        <v>46295.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46285.09375</v>
+        <v>46295.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46285.10416666666</v>
+        <v>46295.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46285.11458333334</v>
+        <v>46295.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46285.125</v>
+        <v>46295.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46285.13541666666</v>
+        <v>46295.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46285.14583333334</v>
+        <v>46295.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46285.15625</v>
+        <v>46295.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46285.16666666666</v>
+        <v>46295.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46285.17708333334</v>
+        <v>46295.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46285.1875</v>
+        <v>46295.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46285.19791666666</v>
+        <v>46295.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46285.20833333334</v>
+        <v>46295.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46285.21875</v>
+        <v>46295.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46285.22916666666</v>
+        <v>46295.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46285.23958333334</v>
+        <v>46295.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46285.25</v>
+        <v>46295.25</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -594,106 +594,114 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46285.26041666666</v>
+        <v>46295.26041666666</v>
       </c>
       <c r="B27">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46285.27083333334</v>
+        <v>46295.27083333334</v>
       </c>
       <c r="B28">
-        <v>85</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46285.28125</v>
+        <v>46295.28125</v>
       </c>
       <c r="B29">
-        <v>187</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46285.29166666666</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="B30">
-        <v>339</v>
+        <v>325</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46285.30208333334</v>
+        <v>46295.30208333334</v>
       </c>
       <c r="B31">
-        <v>529</v>
+        <v>523</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46285.3125</v>
+        <v>46295.3125</v>
       </c>
       <c r="B32">
-        <v>729</v>
+        <v>743</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46285.32291666666</v>
+        <v>46295.32291666666</v>
       </c>
       <c r="B33">
-        <v>938</v>
+        <v>963</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46285.33333333334</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="B34">
-        <v>1097</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46285.34375</v>
+        <v>46295.34375</v>
       </c>
       <c r="B35">
-        <v>1265</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46285.35416666666</v>
+        <v>46295.35416666666</v>
       </c>
       <c r="B36">
-        <v>1424</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46285.36458333334</v>
+        <v>46295.36458333334</v>
       </c>
       <c r="B37">
-        <v>1614</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46285.375</v>
+        <v>46295.375</v>
       </c>
       <c r="B38">
-        <v>1798</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46285.38541666666</v>
+        <v>46295.38541666666</v>
       </c>
       <c r="B39">
-        <v>1912</v>
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="2">
+        <v>46295.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>2468</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -26,9 +26,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -81,12 +78,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -381,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -392,318 +388,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="2">
-        <v>46295</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="2">
-        <v>46295.01041666666</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="2">
-        <v>46295.02083333334</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="2">
-        <v>46295.03125</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="2">
-        <v>46295.04166666666</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="2">
-        <v>46295.05208333334</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="2">
-        <v>46295.0625</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="2">
-        <v>46295.07291666666</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="2">
-        <v>46295.08333333334</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="2">
-        <v>46295.09375</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="2">
-        <v>46295.10416666666</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="2">
-        <v>46295.11458333334</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="2">
-        <v>46295.125</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="2">
-        <v>46295.13541666666</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="2">
-        <v>46295.14583333334</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="2">
-        <v>46295.15625</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="2">
-        <v>46295.16666666666</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="2">
-        <v>46295.17708333334</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="2">
-        <v>46295.1875</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="2">
-        <v>46295.19791666666</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="2">
-        <v>46295.20833333334</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="2">
-        <v>46295.21875</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="2">
-        <v>46295.22916666666</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="2">
-        <v>46295.23958333334</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="2">
-        <v>46295.25</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="2">
-        <v>46295.26041666666</v>
-      </c>
-      <c r="B27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="2">
-        <v>46295.27083333334</v>
-      </c>
-      <c r="B28">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="2">
-        <v>46295.28125</v>
-      </c>
-      <c r="B29">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="2">
-        <v>46295.29166666666</v>
-      </c>
-      <c r="B30">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="2">
-        <v>46295.30208333334</v>
-      </c>
-      <c r="B31">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="2">
-        <v>46295.3125</v>
-      </c>
-      <c r="B32">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="2">
-        <v>46295.32291666666</v>
-      </c>
-      <c r="B33">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="2">
-        <v>46295.33333333334</v>
-      </c>
-      <c r="B34">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="2">
-        <v>46295.34375</v>
-      </c>
-      <c r="B35">
-        <v>1475</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="2">
-        <v>46295.35416666666</v>
-      </c>
-      <c r="B36">
-        <v>1661</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="2">
-        <v>46295.36458333334</v>
-      </c>
-      <c r="B37">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="2">
-        <v>46295.375</v>
-      </c>
-      <c r="B38">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="2">
-        <v>46295.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>2348</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="2">
-        <v>46295.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>2468</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -26,6 +26,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -78,11 +81,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -377,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B425"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -388,6 +392,3398 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2">
+        <v>46298.01041666666</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2">
+        <v>46298.02083333334</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2">
+        <v>46298.03125</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2">
+        <v>46298.04166666666</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2">
+        <v>46298.05208333334</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2">
+        <v>46298.0625</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2">
+        <v>46298.07291666666</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2">
+        <v>46298.08333333334</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2">
+        <v>46298.09375</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2">
+        <v>46298.10416666666</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2">
+        <v>46298.11458333334</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
+        <v>46298.125</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2">
+        <v>46298.13541666666</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2">
+        <v>46298.14583333334</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2">
+        <v>46298.15625</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2">
+        <v>46298.16666666666</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2">
+        <v>46298.17708333334</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2">
+        <v>46298.1875</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2">
+        <v>46298.19791666666</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2">
+        <v>46298.20833333334</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2">
+        <v>46298.21875</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2">
+        <v>46298.22916666666</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2">
+        <v>46298.23958333334</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2">
+        <v>46298.25</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2">
+        <v>46298.26041666666</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="2">
+        <v>46298.27083333334</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="2">
+        <v>46298.28125</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="2">
+        <v>46298.29166666666</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="2">
+        <v>46298.30208333334</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="2">
+        <v>46298.3125</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="2">
+        <v>46298.32291666666</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="2">
+        <v>46298.33333333334</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="2">
+        <v>46298.34375</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="2">
+        <v>46298.35416666666</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2">
+        <v>46298.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2">
+        <v>46298.375</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2">
+        <v>46298.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="2">
+        <v>46298.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="2">
+        <v>46298.40625</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="2">
+        <v>46298.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="2">
+        <v>46298.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="2">
+        <v>46298.4375</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="2">
+        <v>46298.44791666666</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="2">
+        <v>46298.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="2">
+        <v>46298.46875</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="2">
+        <v>46298.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="2">
+        <v>46298.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="2">
+        <v>46298.5</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="2">
+        <v>46298.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="2">
+        <v>46298.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="2">
+        <v>46298.53125</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="2">
+        <v>46298.54166666666</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="2">
+        <v>46298.55208333334</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="2">
+        <v>46298.5625</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="2">
+        <v>46298.57291666666</v>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="2">
+        <v>46298.58333333334</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="2">
+        <v>46298.59375</v>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="2">
+        <v>46298.60416666666</v>
+      </c>
+      <c r="B60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="2">
+        <v>46298.61458333334</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="2">
+        <v>46298.625</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="2">
+        <v>46298.63541666666</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="2">
+        <v>46298.64583333334</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="2">
+        <v>46298.65625</v>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="2">
+        <v>46298.66666666666</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="2">
+        <v>46298.67708333334</v>
+      </c>
+      <c r="B67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="2">
+        <v>46298.6875</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="2">
+        <v>46298.69791666666</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="2">
+        <v>46298.70833333334</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="2">
+        <v>46298.71875</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="2">
+        <v>46298.72916666666</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="2">
+        <v>46298.73958333334</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="2">
+        <v>46298.75</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="2">
+        <v>46298.76041666666</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="2">
+        <v>46298.77083333334</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="2">
+        <v>46298.78125</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="2">
+        <v>46298.79166666666</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="2">
+        <v>46298.80208333334</v>
+      </c>
+      <c r="B79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="2">
+        <v>46298.8125</v>
+      </c>
+      <c r="B80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="2">
+        <v>46298.82291666666</v>
+      </c>
+      <c r="B81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="2">
+        <v>46298.83333333334</v>
+      </c>
+      <c r="B82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="2">
+        <v>46298.84375</v>
+      </c>
+      <c r="B83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="2">
+        <v>46298.85416666666</v>
+      </c>
+      <c r="B84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="2">
+        <v>46298.86458333334</v>
+      </c>
+      <c r="B85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="2">
+        <v>46298.875</v>
+      </c>
+      <c r="B86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="2">
+        <v>46298.88541666666</v>
+      </c>
+      <c r="B87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="2">
+        <v>46298.89583333334</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="2">
+        <v>46298.90625</v>
+      </c>
+      <c r="B89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="2">
+        <v>46298.91666666666</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="2">
+        <v>46298.92708333334</v>
+      </c>
+      <c r="B91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="2">
+        <v>46298.9375</v>
+      </c>
+      <c r="B92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="2">
+        <v>46298.94791666666</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="2">
+        <v>46298.95833333334</v>
+      </c>
+      <c r="B94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="2">
+        <v>46298.96875</v>
+      </c>
+      <c r="B95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="2">
+        <v>46298.97916666666</v>
+      </c>
+      <c r="B96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="2">
+        <v>46298.98958333334</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46299.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46299.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46299.03125</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46299.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46299.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46299.0625</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46299.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46299.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46299.09375</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46299.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46299.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46299.125</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46299.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46299.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46299.15625</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46299.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46299.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46299.1875</v>
+      </c>
+      <c r="B116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46299.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46299.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46299.21875</v>
+      </c>
+      <c r="B119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46299.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46299.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46299.25</v>
+      </c>
+      <c r="B122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46299.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46299.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46299.28125</v>
+      </c>
+      <c r="B125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46299.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46299.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46299.3125</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46299.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46299.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46299.34375</v>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46299.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46299.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46299.375</v>
+      </c>
+      <c r="B134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46299.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46299.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46299.40625</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46299.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46299.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46299.4375</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46299.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46299.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46299.46875</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46299.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46299.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46299.5</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46299.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46299.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46299.53125</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46299.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46299.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46299.5625</v>
+      </c>
+      <c r="B152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46299.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46299.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46299.59375</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46299.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46299.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46299.625</v>
+      </c>
+      <c r="B158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46299.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46299.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46299.65625</v>
+      </c>
+      <c r="B161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46299.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46299.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46299.6875</v>
+      </c>
+      <c r="B164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46299.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46299.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46299.71875</v>
+      </c>
+      <c r="B167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46299.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46299.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46299.75</v>
+      </c>
+      <c r="B170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46299.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46299.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46299.78125</v>
+      </c>
+      <c r="B173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46299.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46299.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46299.8125</v>
+      </c>
+      <c r="B176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46299.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46299.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46299.84375</v>
+      </c>
+      <c r="B179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46299.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46299.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46299.875</v>
+      </c>
+      <c r="B182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46299.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46299.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46299.90625</v>
+      </c>
+      <c r="B185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46299.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46299.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46299.9375</v>
+      </c>
+      <c r="B188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46299.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46299.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46299.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46299.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46299.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="2">
+        <v>46300.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="2">
+        <v>46300.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="2">
+        <v>46300.03125</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2">
+        <v>46300.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="2">
+        <v>46300.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2">
+        <v>46300.0625</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="2">
+        <v>46300.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2">
+        <v>46300.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="2">
+        <v>46300.09375</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="2">
+        <v>46300.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="2">
+        <v>46300.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="2">
+        <v>46300.125</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2">
+        <v>46300.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="2">
+        <v>46300.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="2">
+        <v>46300.15625</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="2">
+        <v>46300.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="2">
+        <v>46300.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="2">
+        <v>46300.1875</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="2">
+        <v>46300.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2">
+        <v>46300.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="2">
+        <v>46300.21875</v>
+      </c>
+      <c r="B215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="2">
+        <v>46300.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="2">
+        <v>46300.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2">
+        <v>46300.25</v>
+      </c>
+      <c r="B218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="2">
+        <v>46300.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="2">
+        <v>46300.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="2">
+        <v>46300.28125</v>
+      </c>
+      <c r="B221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2">
+        <v>46300.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="2">
+        <v>46300.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="2">
+        <v>46300.3125</v>
+      </c>
+      <c r="B224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="2">
+        <v>46300.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="2">
+        <v>46300.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="2">
+        <v>46300.34375</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="2">
+        <v>46300.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="2">
+        <v>46300.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="2">
+        <v>46300.375</v>
+      </c>
+      <c r="B230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="2">
+        <v>46300.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="2">
+        <v>46300.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="2">
+        <v>46300.40625</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="2">
+        <v>46300.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="2">
+        <v>46300.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="2">
+        <v>46300.4375</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="2">
+        <v>46300.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2">
+        <v>46300.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="2">
+        <v>46300.46875</v>
+      </c>
+      <c r="B239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="2">
+        <v>46300.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="2">
+        <v>46300.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="2">
+        <v>46300.5</v>
+      </c>
+      <c r="B242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="2">
+        <v>46300.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="2">
+        <v>46300.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="2">
+        <v>46300.53125</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="2">
+        <v>46300.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="2">
+        <v>46300.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="2">
+        <v>46300.5625</v>
+      </c>
+      <c r="B248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="2">
+        <v>46300.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="2">
+        <v>46300.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="2">
+        <v>46300.59375</v>
+      </c>
+      <c r="B251">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="2">
+        <v>46300.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="2">
+        <v>46300.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="2">
+        <v>46300.625</v>
+      </c>
+      <c r="B254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="2">
+        <v>46300.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="2">
+        <v>46300.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="2">
+        <v>46300.65625</v>
+      </c>
+      <c r="B257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="2">
+        <v>46300.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="2">
+        <v>46300.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2">
+        <v>46300.6875</v>
+      </c>
+      <c r="B260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="2">
+        <v>46300.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="2">
+        <v>46300.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="2">
+        <v>46300.71875</v>
+      </c>
+      <c r="B263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="2">
+        <v>46300.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="2">
+        <v>46300.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="2">
+        <v>46300.75</v>
+      </c>
+      <c r="B266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="2">
+        <v>46300.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="2">
+        <v>46300.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="2">
+        <v>46300.78125</v>
+      </c>
+      <c r="B269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="2">
+        <v>46300.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="2">
+        <v>46300.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="2">
+        <v>46300.8125</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="2">
+        <v>46300.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="2">
+        <v>46300.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2">
+        <v>46300.84375</v>
+      </c>
+      <c r="B275">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="2">
+        <v>46300.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="2">
+        <v>46300.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="2">
+        <v>46300.875</v>
+      </c>
+      <c r="B278">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="2">
+        <v>46300.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="2">
+        <v>46300.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="2">
+        <v>46300.90625</v>
+      </c>
+      <c r="B281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="2">
+        <v>46300.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="2">
+        <v>46300.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="2">
+        <v>46300.9375</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="2">
+        <v>46300.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="2">
+        <v>46300.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="2">
+        <v>46300.96875</v>
+      </c>
+      <c r="B287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="2">
+        <v>46300.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="2">
+        <v>46300.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="2">
+        <v>46301.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="2">
+        <v>46301.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="2">
+        <v>46301.03125</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="2">
+        <v>46301.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="2">
+        <v>46301.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="2">
+        <v>46301.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="2">
+        <v>46301.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="2">
+        <v>46301.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="2">
+        <v>46301.09375</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="2">
+        <v>46301.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="2">
+        <v>46301.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="2">
+        <v>46301.125</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="2">
+        <v>46301.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="2">
+        <v>46301.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="2">
+        <v>46301.15625</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="2">
+        <v>46301.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="2">
+        <v>46301.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2">
+        <v>46301.1875</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="2">
+        <v>46301.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="2">
+        <v>46301.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="2">
+        <v>46301.21875</v>
+      </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2">
+        <v>46301.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="2">
+        <v>46301.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="2">
+        <v>46301.25</v>
+      </c>
+      <c r="B314">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="2">
+        <v>46301.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="2">
+        <v>46301.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="2">
+        <v>46301.28125</v>
+      </c>
+      <c r="B317">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="2">
+        <v>46301.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="2">
+        <v>46301.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="2">
+        <v>46301.3125</v>
+      </c>
+      <c r="B320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="2">
+        <v>46301.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="2">
+        <v>46301.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="2">
+        <v>46301.34375</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="2">
+        <v>46301.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="2">
+        <v>46301.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="2">
+        <v>46301.375</v>
+      </c>
+      <c r="B326">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="2">
+        <v>46301.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="2">
+        <v>46301.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="2">
+        <v>46301.40625</v>
+      </c>
+      <c r="B329">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="2">
+        <v>46301.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>2628</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="2">
+        <v>46301.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>2688</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="2">
+        <v>46301.4375</v>
+      </c>
+      <c r="B332">
+        <v>2743</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="2">
+        <v>46301.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>2808</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="2">
+        <v>46301.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="2">
+        <v>46301.46875</v>
+      </c>
+      <c r="B335">
+        <v>2935</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="2">
+        <v>46301.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="2">
+        <v>46301.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>2978</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="2">
+        <v>46301.5</v>
+      </c>
+      <c r="B338">
+        <v>2943</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="2">
+        <v>46301.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>2904</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="2">
+        <v>46301.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>2878</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="2">
+        <v>46301.53125</v>
+      </c>
+      <c r="B341">
+        <v>2884</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="2">
+        <v>46301.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="2">
+        <v>46301.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>2874</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="2">
+        <v>46301.5625</v>
+      </c>
+      <c r="B344">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="2">
+        <v>46301.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>2696</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="2">
+        <v>46301.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>2688</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="2">
+        <v>46301.59375</v>
+      </c>
+      <c r="B347">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="2">
+        <v>46301.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="2">
+        <v>46301.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="2">
+        <v>46301.625</v>
+      </c>
+      <c r="B350">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="2">
+        <v>46301.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="2">
+        <v>46301.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="2">
+        <v>46301.65625</v>
+      </c>
+      <c r="B353">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="2">
+        <v>46301.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="2">
+        <v>46301.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="2">
+        <v>46301.6875</v>
+      </c>
+      <c r="B356">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="2">
+        <v>46301.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="2">
+        <v>46301.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="2">
+        <v>46301.71875</v>
+      </c>
+      <c r="B359">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="2">
+        <v>46301.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="2">
+        <v>46301.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="2">
+        <v>46301.75</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="2">
+        <v>46301.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="2">
+        <v>46301.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="2">
+        <v>46301.78125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="2">
+        <v>46301.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="2">
+        <v>46301.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="2">
+        <v>46301.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="2">
+        <v>46301.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="2">
+        <v>46301.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="2">
+        <v>46301.84375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="2">
+        <v>46301.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="2">
+        <v>46301.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="2">
+        <v>46301.875</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="2">
+        <v>46301.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="2">
+        <v>46301.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="2">
+        <v>46301.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="2">
+        <v>46301.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="2">
+        <v>46301.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="2">
+        <v>46301.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="2">
+        <v>46301.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="2">
+        <v>46301.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="2">
+        <v>46301.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="2">
+        <v>46301.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="2">
+        <v>46301.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="2">
+        <v>46302.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="2">
+        <v>46302.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" s="2">
+        <v>46302.03125</v>
+      </c>
+      <c r="B389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" s="2">
+        <v>46302.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="2">
+        <v>46302.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="2">
+        <v>46302.0625</v>
+      </c>
+      <c r="B392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" s="2">
+        <v>46302.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="2">
+        <v>46302.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="2">
+        <v>46302.09375</v>
+      </c>
+      <c r="B395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="2">
+        <v>46302.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="2">
+        <v>46302.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="2">
+        <v>46302.125</v>
+      </c>
+      <c r="B398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="2">
+        <v>46302.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="2">
+        <v>46302.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="2">
+        <v>46302.15625</v>
+      </c>
+      <c r="B401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" s="2">
+        <v>46302.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" s="2">
+        <v>46302.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="2">
+        <v>46302.1875</v>
+      </c>
+      <c r="B404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" s="2">
+        <v>46302.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="2">
+        <v>46302.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" s="2">
+        <v>46302.21875</v>
+      </c>
+      <c r="B407">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" s="2">
+        <v>46302.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="2">
+        <v>46302.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" s="2">
+        <v>46302.25</v>
+      </c>
+      <c r="B410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" s="2">
+        <v>46302.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" s="2">
+        <v>46302.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" s="2">
+        <v>46302.28125</v>
+      </c>
+      <c r="B413">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="2">
+        <v>46302.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" s="2">
+        <v>46302.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="2">
+        <v>46302.3125</v>
+      </c>
+      <c r="B416">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="2">
+        <v>46302.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" s="2">
+        <v>46302.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="2">
+        <v>46302.34375</v>
+      </c>
+      <c r="B419">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" s="2">
+        <v>46302.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" s="2">
+        <v>46302.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" s="2">
+        <v>46302.375</v>
+      </c>
+      <c r="B422">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" s="2">
+        <v>46302.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="2">
+        <v>46302.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" s="2">
+        <v>46302.40625</v>
+      </c>
+      <c r="B425">
+        <v>2503</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B133"/>
+  <dimension ref="A1:B132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46302.01041666666</v>
+        <v>46303.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46302.02083333334</v>
+        <v>46303.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46302.03125</v>
+        <v>46303.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46302.04166666666</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46302.05208333334</v>
+        <v>46303.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46302.0625</v>
+        <v>46303.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46302.07291666666</v>
+        <v>46303.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46302.08333333334</v>
+        <v>46303.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46302.09375</v>
+        <v>46303.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46302.10416666666</v>
+        <v>46303.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46302.11458333334</v>
+        <v>46303.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46302.125</v>
+        <v>46303.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46302.13541666666</v>
+        <v>46303.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46302.14583333334</v>
+        <v>46303.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46302.15625</v>
+        <v>46303.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46302.16666666666</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46302.17708333334</v>
+        <v>46303.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46302.1875</v>
+        <v>46303.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46302.19791666666</v>
+        <v>46303.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46302.20833333334</v>
+        <v>46303.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46302.21875</v>
+        <v>46303.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46302.22916666666</v>
+        <v>46303.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46302.23958333334</v>
+        <v>46303.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46302.26041666666</v>
+        <v>46303.26041666666</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -602,375 +602,375 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46302.27083333334</v>
+        <v>46303.27083333334</v>
       </c>
       <c r="B28">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46302.28125</v>
+        <v>46303.28125</v>
       </c>
       <c r="B29">
-        <v>111</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46302.29166666666</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="B30">
-        <v>270</v>
+        <v>212</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46302.30208333334</v>
+        <v>46303.30208333334</v>
       </c>
       <c r="B31">
-        <v>490</v>
+        <v>379</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46302.3125</v>
+        <v>46303.3125</v>
       </c>
       <c r="B32">
-        <v>731</v>
+        <v>566</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46302.32291666666</v>
+        <v>46303.32291666666</v>
       </c>
       <c r="B33">
-        <v>976</v>
+        <v>758</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46302.33333333334</v>
+        <v>46303.33333333334</v>
       </c>
       <c r="B34">
-        <v>1231</v>
+        <v>994</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46302.34375</v>
+        <v>46303.34375</v>
       </c>
       <c r="B35">
-        <v>1504</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46302.35416666666</v>
+        <v>46303.35416666666</v>
       </c>
       <c r="B36">
-        <v>1719</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46302.36458333334</v>
+        <v>46303.36458333334</v>
       </c>
       <c r="B37">
-        <v>1901</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46302.375</v>
+        <v>46303.375</v>
       </c>
       <c r="B38">
-        <v>2079</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46302.38541666666</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="B39">
-        <v>2248</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46302.39583333334</v>
+        <v>46303.39583333334</v>
       </c>
       <c r="B40">
-        <v>2401</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46302.40625</v>
+        <v>46303.40625</v>
       </c>
       <c r="B41">
-        <v>2503</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46302.41666666666</v>
+        <v>46303.41666666666</v>
       </c>
       <c r="B42">
-        <v>2578</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46302.42708333334</v>
+        <v>46303.42708333334</v>
       </c>
       <c r="B43">
-        <v>2650</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46302.4375</v>
+        <v>46303.4375</v>
       </c>
       <c r="B44">
-        <v>2677</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46302.44791666666</v>
+        <v>46303.44791666666</v>
       </c>
       <c r="B45">
-        <v>2741</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46302.45833333334</v>
+        <v>46303.45833333334</v>
       </c>
       <c r="B46">
-        <v>2756</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46302.46875</v>
+        <v>46303.46875</v>
       </c>
       <c r="B47">
-        <v>2770</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46302.47916666666</v>
+        <v>46303.47916666666</v>
       </c>
       <c r="B48">
-        <v>2795</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46302.48958333334</v>
+        <v>46303.48958333334</v>
       </c>
       <c r="B49">
-        <v>2801</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46302.5</v>
+        <v>46303.5</v>
       </c>
       <c r="B50">
-        <v>2774</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46302.51041666666</v>
+        <v>46303.51041666666</v>
       </c>
       <c r="B51">
-        <v>2758</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46302.52083333334</v>
+        <v>46303.52083333334</v>
       </c>
       <c r="B52">
-        <v>2740</v>
+        <v>2815</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46302.53125</v>
+        <v>46303.53125</v>
       </c>
       <c r="B53">
-        <v>2726</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46302.54166666666</v>
+        <v>46303.54166666666</v>
       </c>
       <c r="B54">
-        <v>2715</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46302.55208333334</v>
+        <v>46303.55208333334</v>
       </c>
       <c r="B55">
-        <v>2635</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46302.5625</v>
+        <v>46303.5625</v>
       </c>
       <c r="B56">
-        <v>2626</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46302.57291666666</v>
+        <v>46303.57291666666</v>
       </c>
       <c r="B57">
-        <v>2557</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46302.58333333334</v>
+        <v>46303.58333333334</v>
       </c>
       <c r="B58">
-        <v>2432</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46302.59375</v>
+        <v>46303.59375</v>
       </c>
       <c r="B59">
-        <v>2354</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46302.60416666666</v>
+        <v>46303.60416666666</v>
       </c>
       <c r="B60">
-        <v>2254</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46302.61458333334</v>
+        <v>46303.61458333334</v>
       </c>
       <c r="B61">
-        <v>2163</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46302.625</v>
+        <v>46303.625</v>
       </c>
       <c r="B62">
-        <v>1944</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46302.63541666666</v>
+        <v>46303.63541666666</v>
       </c>
       <c r="B63">
-        <v>1701</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46302.64583333334</v>
+        <v>46303.64583333334</v>
       </c>
       <c r="B64">
-        <v>1518</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46302.65625</v>
+        <v>46303.65625</v>
       </c>
       <c r="B65">
-        <v>1331</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46302.66666666666</v>
+        <v>46303.66666666666</v>
       </c>
       <c r="B66">
-        <v>1043</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46302.67708333334</v>
+        <v>46303.67708333334</v>
       </c>
       <c r="B67">
-        <v>821</v>
+        <v>906</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46302.6875</v>
+        <v>46303.6875</v>
       </c>
       <c r="B68">
-        <v>625</v>
+        <v>676</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46302.69791666666</v>
+        <v>46303.69791666666</v>
       </c>
       <c r="B69">
-        <v>435</v>
+        <v>470</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46302.70833333334</v>
+        <v>46303.70833333334</v>
       </c>
       <c r="B70">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46302.71875</v>
+        <v>46303.71875</v>
       </c>
       <c r="B71">
-        <v>139</v>
+        <v>106</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46302.72916666666</v>
+        <v>46303.72916666666</v>
       </c>
       <c r="B72">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46302.73958333334</v>
+        <v>46303.73958333334</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46302.75</v>
+        <v>46303.75</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46302.76041666666</v>
+        <v>46303.76041666666</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46302.77083333334</v>
+        <v>46303.77083333334</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46302.78125</v>
+        <v>46303.78125</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46302.79166666666</v>
+        <v>46303.79166666666</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46302.80208333334</v>
+        <v>46303.80208333334</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46302.8125</v>
+        <v>46303.8125</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46302.82291666666</v>
+        <v>46303.82291666666</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46302.83333333334</v>
+        <v>46303.83333333334</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46302.84375</v>
+        <v>46303.84375</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46302.85416666666</v>
+        <v>46303.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46302.86458333334</v>
+        <v>46303.86458333334</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46302.875</v>
+        <v>46303.875</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46302.88541666666</v>
+        <v>46303.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46302.89583333334</v>
+        <v>46303.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46302.90625</v>
+        <v>46303.90625</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46302.91666666666</v>
+        <v>46303.91666666666</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46302.92708333334</v>
+        <v>46303.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46302.9375</v>
+        <v>46303.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46302.94791666666</v>
+        <v>46303.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46302.95833333334</v>
+        <v>46303.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46302.96875</v>
+        <v>46303.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46302.97916666666</v>
+        <v>46303.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46302.98958333334</v>
+        <v>46303.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1258,7 +1258,7 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1298,7 +1298,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -1322,7 +1322,7 @@
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -1338,7 +1338,7 @@
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B124">
         <v>18</v>
@@ -1378,74 +1378,66 @@
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B125">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B126">
-        <v>212</v>
+        <v>194</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B127">
-        <v>379</v>
+        <v>321</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B128">
-        <v>566</v>
+        <v>506</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B129">
-        <v>758</v>
+        <v>667</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B130">
-        <v>994</v>
+        <v>872</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B131">
-        <v>1252</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B132">
-        <v>1488</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="2">
-        <v>46303.36458333334</v>
-      </c>
-      <c r="B133">
-        <v>1723</v>
+        <v>1323</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46307.01041666666</v>
+        <v>46308.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46307.02083333334</v>
+        <v>46308.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46307.03125</v>
+        <v>46308.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46307.04166666666</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46307.05208333334</v>
+        <v>46308.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46307.0625</v>
+        <v>46308.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46307.07291666666</v>
+        <v>46308.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46307.08333333334</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46307.09375</v>
+        <v>46308.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46307.10416666666</v>
+        <v>46308.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46307.11458333334</v>
+        <v>46308.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46307.125</v>
+        <v>46308.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46307.13541666666</v>
+        <v>46308.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46307.14583333334</v>
+        <v>46308.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46307.15625</v>
+        <v>46308.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46307.16666666666</v>
+        <v>46308.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46307.17708333334</v>
+        <v>46308.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46307.1875</v>
+        <v>46308.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46307.19791666666</v>
+        <v>46308.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46307.20833333334</v>
+        <v>46308.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46307.21875</v>
+        <v>46308.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46307.22916666666</v>
+        <v>46308.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46307.23958333334</v>
+        <v>46308.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46307.26041666666</v>
+        <v>46308.26041666666</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -602,7 +602,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46307.27083333334</v>
+        <v>46308.27083333334</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -610,7 +610,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46307.28125</v>
+        <v>46308.28125</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -618,90 +618,218 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46307.29166666666</v>
+        <v>46308.29166666666</v>
       </c>
       <c r="B30">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46307.30208333334</v>
+        <v>46308.30208333334</v>
       </c>
       <c r="B31">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46307.3125</v>
+        <v>46308.3125</v>
       </c>
       <c r="B32">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46307.32291666666</v>
+        <v>46308.32291666666</v>
       </c>
       <c r="B33">
-        <v>180</v>
+        <v>207</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46307.33333333334</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="B34">
-        <v>252</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46307.34375</v>
+        <v>46308.34375</v>
       </c>
       <c r="B35">
-        <v>315</v>
+        <v>405</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46307.35416666666</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="B36">
-        <v>398</v>
+        <v>487</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46307.36458333334</v>
+        <v>46308.36458333334</v>
       </c>
       <c r="B37">
-        <v>461</v>
+        <v>583</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46307.375</v>
+        <v>46308.375</v>
       </c>
       <c r="B38">
-        <v>547</v>
+        <v>689</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46307.38541666666</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="B39">
-        <v>594</v>
+        <v>772</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46307.39583333334</v>
+        <v>46308.39583333334</v>
       </c>
       <c r="B40">
-        <v>684</v>
+        <v>842</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="2">
+        <v>46308.40625</v>
+      </c>
+      <c r="B41">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="2">
+        <v>46308.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="2">
+        <v>46308.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="2">
+        <v>46308.4375</v>
+      </c>
+      <c r="B44">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="2">
+        <v>46308.44791666666</v>
+      </c>
+      <c r="B45">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="2">
+        <v>46308.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="2">
+        <v>46308.46875</v>
+      </c>
+      <c r="B47">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="2">
+        <v>46308.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="2">
+        <v>46308.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="2">
+        <v>46308.5</v>
+      </c>
+      <c r="B50">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="2">
+        <v>46308.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="2">
+        <v>46308.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="2">
+        <v>46308.53125</v>
+      </c>
+      <c r="B53">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="2">
+        <v>46308.54166666666</v>
+      </c>
+      <c r="B54">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="2">
+        <v>46308.55208333334</v>
+      </c>
+      <c r="B55">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="2">
+        <v>46308.5625</v>
+      </c>
+      <c r="B56">
+        <v>1183</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46308.01041666666</v>
+        <v>46309.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46308.02083333334</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46308.03125</v>
+        <v>46309.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46308.04166666666</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46308.05208333334</v>
+        <v>46309.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46308.0625</v>
+        <v>46309.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46308.07291666666</v>
+        <v>46309.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46308.08333333334</v>
+        <v>46309.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46308.09375</v>
+        <v>46309.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46308.10416666666</v>
+        <v>46309.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46308.11458333334</v>
+        <v>46309.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46308.125</v>
+        <v>46309.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46308.13541666666</v>
+        <v>46309.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46308.14583333334</v>
+        <v>46309.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46308.15625</v>
+        <v>46309.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46308.16666666666</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46308.17708333334</v>
+        <v>46309.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46308.1875</v>
+        <v>46309.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46308.19791666666</v>
+        <v>46309.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46308.20833333334</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46308.21875</v>
+        <v>46309.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46308.22916666666</v>
+        <v>46309.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46308.23958333334</v>
+        <v>46309.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46308.26041666666</v>
+        <v>46309.26041666666</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -602,7 +602,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46308.27083333334</v>
+        <v>46309.27083333334</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -610,226 +610,258 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46308.28125</v>
+        <v>46309.28125</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46308.29166666666</v>
+        <v>46309.29166666666</v>
       </c>
       <c r="B30">
-        <v>27</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46308.30208333334</v>
+        <v>46309.30208333334</v>
       </c>
       <c r="B31">
-        <v>63</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46308.3125</v>
+        <v>46309.3125</v>
       </c>
       <c r="B32">
-        <v>128</v>
+        <v>281</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46308.32291666666</v>
+        <v>46309.32291666666</v>
       </c>
       <c r="B33">
-        <v>207</v>
+        <v>411</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46308.33333333334</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="B34">
-        <v>305</v>
+        <v>563</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46308.34375</v>
+        <v>46309.34375</v>
       </c>
       <c r="B35">
-        <v>405</v>
+        <v>705</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46308.35416666666</v>
+        <v>46309.35416666666</v>
       </c>
       <c r="B36">
-        <v>487</v>
+        <v>915</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46308.36458333334</v>
+        <v>46309.36458333334</v>
       </c>
       <c r="B37">
-        <v>583</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46308.375</v>
+        <v>46309.375</v>
       </c>
       <c r="B38">
-        <v>689</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46308.38541666666</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="B39">
-        <v>772</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46308.39583333334</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="B40">
-        <v>842</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46308.40625</v>
+        <v>46309.40625</v>
       </c>
       <c r="B41">
-        <v>944</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46308.41666666666</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="B42">
-        <v>989</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46308.42708333334</v>
+        <v>46309.42708333334</v>
       </c>
       <c r="B43">
-        <v>1037</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46308.4375</v>
+        <v>46309.4375</v>
       </c>
       <c r="B44">
-        <v>1103</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46308.44791666666</v>
+        <v>46309.44791666666</v>
       </c>
       <c r="B45">
-        <v>1199</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46308.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="B46">
-        <v>1288</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46308.46875</v>
+        <v>46309.46875</v>
       </c>
       <c r="B47">
-        <v>1402</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46308.47916666666</v>
+        <v>46309.47916666666</v>
       </c>
       <c r="B48">
-        <v>1501</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46308.48958333334</v>
+        <v>46309.48958333334</v>
       </c>
       <c r="B49">
-        <v>1520</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="B50">
-        <v>1536</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46308.51041666666</v>
+        <v>46309.51041666666</v>
       </c>
       <c r="B51">
-        <v>1529</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46308.52083333334</v>
+        <v>46309.52083333334</v>
       </c>
       <c r="B52">
-        <v>1462</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46308.53125</v>
+        <v>46309.53125</v>
       </c>
       <c r="B53">
-        <v>1375</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46308.54166666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="B54">
-        <v>1235</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46308.55208333334</v>
+        <v>46309.55208333334</v>
       </c>
       <c r="B55">
-        <v>1224</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46308.5625</v>
+        <v>46309.5625</v>
       </c>
       <c r="B56">
-        <v>1183</v>
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="2">
+        <v>46309.57291666666</v>
+      </c>
+      <c r="B57">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="2">
+        <v>46309.58333333334</v>
+      </c>
+      <c r="B58">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="2">
+        <v>46309.59375</v>
+      </c>
+      <c r="B59">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="2">
+        <v>46309.60416666666</v>
+      </c>
+      <c r="B60">
+        <v>2132</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46309.01041666666</v>
+        <v>46311.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46309.02083333334</v>
+        <v>46311.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46309.03125</v>
+        <v>46311.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46309.04166666666</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46309.05208333334</v>
+        <v>46311.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46309.0625</v>
+        <v>46311.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46309.07291666666</v>
+        <v>46311.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46309.08333333334</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46309.09375</v>
+        <v>46311.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46309.10416666666</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46309.11458333334</v>
+        <v>46311.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46309.125</v>
+        <v>46311.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46309.13541666666</v>
+        <v>46311.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46309.14583333334</v>
+        <v>46311.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46309.15625</v>
+        <v>46311.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46309.16666666666</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46309.17708333334</v>
+        <v>46311.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46309.1875</v>
+        <v>46311.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46309.19791666666</v>
+        <v>46311.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46309.20833333334</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46309.21875</v>
+        <v>46311.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46309.22916666666</v>
+        <v>46311.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46309.23958333334</v>
+        <v>46311.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46309.25</v>
+        <v>46311.25</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46309.26041666666</v>
+        <v>46311.26041666666</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -602,7 +602,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46309.27083333334</v>
+        <v>46311.27083333334</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -610,258 +610,194 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46309.28125</v>
+        <v>46311.28125</v>
       </c>
       <c r="B29">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46309.29166666666</v>
+        <v>46311.29166666666</v>
       </c>
       <c r="B30">
-        <v>81</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46309.30208333334</v>
+        <v>46311.30208333334</v>
       </c>
       <c r="B31">
-        <v>165</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46309.3125</v>
+        <v>46311.3125</v>
       </c>
       <c r="B32">
-        <v>281</v>
+        <v>229</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46309.32291666666</v>
+        <v>46311.32291666666</v>
       </c>
       <c r="B33">
-        <v>411</v>
+        <v>326</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46309.33333333334</v>
+        <v>46311.33333333334</v>
       </c>
       <c r="B34">
-        <v>563</v>
+        <v>436</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46309.34375</v>
+        <v>46311.34375</v>
       </c>
       <c r="B35">
-        <v>705</v>
+        <v>598</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46309.35416666666</v>
+        <v>46311.35416666666</v>
       </c>
       <c r="B36">
-        <v>915</v>
+        <v>715</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46309.36458333334</v>
+        <v>46311.36458333334</v>
       </c>
       <c r="B37">
-        <v>1111</v>
+        <v>829</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46309.375</v>
+        <v>46311.375</v>
       </c>
       <c r="B38">
-        <v>1261</v>
+        <v>977</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46309.38541666666</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="B39">
-        <v>1384</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46309.39583333334</v>
+        <v>46311.39583333334</v>
       </c>
       <c r="B40">
-        <v>1497</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46309.40625</v>
+        <v>46311.40625</v>
       </c>
       <c r="B41">
-        <v>1653</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46309.41666666666</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="B42">
-        <v>1829</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46309.42708333334</v>
+        <v>46311.42708333334</v>
       </c>
       <c r="B43">
-        <v>2016</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46309.4375</v>
+        <v>46311.4375</v>
       </c>
       <c r="B44">
-        <v>2084</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46309.44791666666</v>
+        <v>46311.44791666666</v>
       </c>
       <c r="B45">
-        <v>2182</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46309.45833333334</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="B46">
-        <v>2179</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46309.46875</v>
+        <v>46311.46875</v>
       </c>
       <c r="B47">
-        <v>2294</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46309.47916666666</v>
+        <v>46311.47916666666</v>
       </c>
       <c r="B48">
-        <v>2311</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46309.48958333334</v>
+        <v>46311.48958333334</v>
       </c>
       <c r="B49">
-        <v>2196</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="B50">
-        <v>2155</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46309.51041666666</v>
+        <v>46311.51041666666</v>
       </c>
       <c r="B51">
-        <v>2235</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46309.52083333334</v>
+        <v>46311.52083333334</v>
       </c>
       <c r="B52">
-        <v>2241</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="2">
-        <v>46309.53125</v>
-      </c>
-      <c r="B53">
-        <v>2182</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="2">
-        <v>46309.54166666666</v>
-      </c>
-      <c r="B54">
-        <v>2194</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="2">
-        <v>46309.55208333334</v>
-      </c>
-      <c r="B55">
-        <v>2199</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="2">
-        <v>46309.5625</v>
-      </c>
-      <c r="B56">
-        <v>2236</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="2">
-        <v>46309.57291666666</v>
-      </c>
-      <c r="B57">
-        <v>2196</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="2">
-        <v>46309.58333333334</v>
-      </c>
-      <c r="B58">
-        <v>2133</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="2">
-        <v>46309.59375</v>
-      </c>
-      <c r="B59">
-        <v>2138</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="2">
-        <v>46309.60416666666</v>
-      </c>
-      <c r="B60">
-        <v>2132</v>
+        <v>1922</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46311.01041666666</v>
+        <v>46316.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46311.02083333334</v>
+        <v>46316.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46311.03125</v>
+        <v>46316.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46311.04166666666</v>
+        <v>46316.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46311.05208333334</v>
+        <v>46316.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46311.0625</v>
+        <v>46316.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46311.07291666666</v>
+        <v>46316.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46311.08333333334</v>
+        <v>46316.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46311.09375</v>
+        <v>46316.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46311.10416666666</v>
+        <v>46316.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46311.11458333334</v>
+        <v>46316.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46311.125</v>
+        <v>46316.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46311.13541666666</v>
+        <v>46316.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46311.14583333334</v>
+        <v>46316.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46311.15625</v>
+        <v>46316.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46311.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46311.17708333334</v>
+        <v>46316.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46311.1875</v>
+        <v>46316.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46311.19791666666</v>
+        <v>46316.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46311.20833333334</v>
+        <v>46316.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46311.21875</v>
+        <v>46316.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46311.22916666666</v>
+        <v>46316.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46311.23958333334</v>
+        <v>46316.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46311.25</v>
+        <v>46316.25</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46311.26041666666</v>
+        <v>46316.26041666666</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -602,7 +602,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46311.27083333334</v>
+        <v>46316.27083333334</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -610,194 +610,66 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46311.28125</v>
+        <v>46316.28125</v>
       </c>
       <c r="B29">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46311.29166666666</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="B30">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46311.30208333334</v>
+        <v>46316.30208333334</v>
       </c>
       <c r="B31">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46311.3125</v>
+        <v>46316.3125</v>
       </c>
       <c r="B32">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46311.32291666666</v>
+        <v>46316.32291666666</v>
       </c>
       <c r="B33">
-        <v>326</v>
+        <v>350</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46311.33333333334</v>
+        <v>46316.33333333334</v>
       </c>
       <c r="B34">
-        <v>436</v>
+        <v>508</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46311.34375</v>
+        <v>46316.34375</v>
       </c>
       <c r="B35">
-        <v>598</v>
+        <v>681</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46311.35416666666</v>
+        <v>46316.35416666666</v>
       </c>
       <c r="B36">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="2">
-        <v>46311.36458333334</v>
-      </c>
-      <c r="B37">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="2">
-        <v>46311.375</v>
-      </c>
-      <c r="B38">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="2">
-        <v>46311.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>1109</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="2">
-        <v>46311.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="2">
-        <v>46311.40625</v>
-      </c>
-      <c r="B41">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="2">
-        <v>46311.41666666666</v>
-      </c>
-      <c r="B42">
-        <v>1391</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="2">
-        <v>46311.42708333334</v>
-      </c>
-      <c r="B43">
-        <v>1538</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="2">
-        <v>46311.4375</v>
-      </c>
-      <c r="B44">
-        <v>1657</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="2">
-        <v>46311.44791666666</v>
-      </c>
-      <c r="B45">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="2">
-        <v>46311.45833333334</v>
-      </c>
-      <c r="B46">
-        <v>1848</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="2">
-        <v>46311.46875</v>
-      </c>
-      <c r="B47">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="2">
-        <v>46311.47916666666</v>
-      </c>
-      <c r="B48">
-        <v>1978</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="2">
-        <v>46311.48958333334</v>
-      </c>
-      <c r="B49">
-        <v>2153</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="2">
-        <v>46311.5</v>
-      </c>
-      <c r="B50">
-        <v>2124</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="2">
-        <v>46311.51041666666</v>
-      </c>
-      <c r="B51">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="2">
-        <v>46311.52083333334</v>
-      </c>
-      <c r="B52">
-        <v>1922</v>
+        <v>814</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46316.01041666666</v>
+        <v>46320.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46316.02083333334</v>
+        <v>46320.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46316.03125</v>
+        <v>46320.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46316.04166666666</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46316.05208333334</v>
+        <v>46320.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46316.0625</v>
+        <v>46320.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46316.07291666666</v>
+        <v>46320.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46316.08333333334</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46316.09375</v>
+        <v>46320.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46316.10416666666</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46316.11458333334</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46316.125</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46316.13541666666</v>
+        <v>46320.09375</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46316.14583333334</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46316.15625</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46316.16666666666</v>
+        <v>46320.125</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46316.17708333334</v>
+        <v>46320.13541666666</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46316.1875</v>
+        <v>46320.14583333334</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46316.19791666666</v>
+        <v>46320.15625</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46316.20833333334</v>
+        <v>46320.16666666666</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46316.21875</v>
+        <v>46320.17708333334</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46316.22916666666</v>
+        <v>46320.1875</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46316.23958333334</v>
+        <v>46320.19791666666</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46316.25</v>
+        <v>46320.20833333334</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46316.26041666666</v>
+        <v>46320.21875</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -602,7 +602,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46316.27083333334</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -610,7 +610,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46316.28125</v>
+        <v>46320.23958333334</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -618,58 +618,82 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46316.29166666666</v>
+        <v>46320.25</v>
       </c>
       <c r="B30">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46316.30208333334</v>
+        <v>46320.26041666666</v>
       </c>
       <c r="B31">
-        <v>115</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46316.3125</v>
+        <v>46320.27083333334</v>
       </c>
       <c r="B32">
-        <v>228</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46316.32291666666</v>
+        <v>46320.28125</v>
       </c>
       <c r="B33">
-        <v>350</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46316.33333333334</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="B34">
-        <v>508</v>
+        <v>367</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46316.34375</v>
+        <v>46320.30208333334</v>
       </c>
       <c r="B35">
-        <v>681</v>
+        <v>494</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46316.35416666666</v>
+        <v>46320.3125</v>
       </c>
       <c r="B36">
-        <v>814</v>
+        <v>598</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2">
+        <v>46320.32291666666</v>
+      </c>
+      <c r="B37">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2">
+        <v>46320.33333333334</v>
+      </c>
+      <c r="B38">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2">
+        <v>46320.34375</v>
+      </c>
+      <c r="B39">
+        <v>915</v>
       </c>
     </row>
   </sheetData>
